--- a/src/flychams_common/config/Configuration-Single-Agent.xlsx
+++ b/src/flychams_common/config/Configuration-Single-Agent.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -355,7 +355,7 @@
     <t xml:space="preserve">CAM02</t>
   </si>
   <si>
-    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT03/MULTICAMERA09</t>
+    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT01/MULTICAMERA03</t>
   </si>
   <si>
     <t xml:space="preserve">Resolution [pix]</t>

--- a/src/flychams_common/config/Configuration-Single-Agent.xlsx
+++ b/src/flychams_common/config/Configuration-Single-Agent.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -376,7 +376,7 @@
     <t xml:space="preserve">Tracking Window 1 Multi-Window (2 Windows)</t>
   </si>
   <si>
-    <t xml:space="preserve">(240x135)</t>
+    <t xml:space="preserve">(480x270)</t>
   </si>
   <si>
     <t xml:space="preserve">MULTIWINDOW01</t>
@@ -496,7 +496,7 @@
     <t xml:space="preserve">High-Resolution Central Camera</t>
   </si>
   <si>
-    <t xml:space="preserve">(1920x1080)</t>
+    <t xml:space="preserve">(3840x2160)</t>
   </si>
   <si>
     <t xml:space="preserve">(-0.08, 0.008, 0.0001, 0.002, -0.0015)</t>
@@ -544,7 +544,7 @@
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -612,6 +612,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -705,7 +711,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -782,6 +788,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -791,6 +801,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1538,92 +1552,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>145</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="21" t="b">
+      <c r="C3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="21" t="b">
+      <c r="E3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="G3" s="21" t="b">
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="I3" s="21" t="n">
+      <c r="I3" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2863,7 +2877,7 @@
       <c r="C3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>115</v>
       </c>
       <c r="E3" s="18" t="n">
@@ -2886,7 +2900,7 @@
       <c r="C4" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>115</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -2953,140 +2967,140 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="21" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D3" s="21" t="n">
+      <c r="D3" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="21" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="H3" s="21" t="b">
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="J3" s="21" t="b">
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="L3" s="21" t="b">
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="N3" s="21" t="n">
+      <c r="N3" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="21" t="n">
+      <c r="O3" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="21" t="n">
+      <c r="P3" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="21" t="n">
+      <c r="Q3" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="21" t="n">
+      <c r="R3" s="22" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3146,52 +3160,52 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>145</v>
       </c>
       <c r="XFB2" s="3"/>
@@ -3199,110 +3213,110 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="21" t="b">
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="21" t="n">
+      <c r="I3" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="G4" s="21" t="b">
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="I4" s="21" t="n">
+      <c r="I4" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="21" t="b">
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="22" t="n">
         <v>5</v>
       </c>
     </row>

--- a/src/flychams_common/config/Configuration-Single-Agent.xlsx
+++ b/src/flychams_common/config/Configuration-Single-Agent.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -64,6 +64,9 @@
     <t xml:space="preserve">StartHour</t>
   </si>
   <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
     <t xml:space="preserve">MISSION00</t>
   </si>
   <si>
@@ -92,9 +95,6 @@
   </si>
   <si>
     <t xml:space="preserve">(16:30:00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X</t>
   </si>
   <si>
     <t xml:space="preserve">MISSION01</t>
@@ -607,17 +607,18 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="2" tint="-0.75"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -711,7 +712,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -744,7 +745,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -756,12 +757,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -788,10 +793,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -801,10 +802,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1353,36 +1350,38 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="B3" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -1431,9 +1430,7 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="A4" s="13"/>
       <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
@@ -1441,28 +1438,28 @@
         <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -1691,12 +1688,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -1718,7 +1715,7 @@
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>27</v>
@@ -1726,7 +1723,7 @@
       <c r="C3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1740,7 +1737,7 @@
       <c r="C4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1780,15 +1777,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -1884,7 +1881,7 @@
       <c r="D3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="16" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -1965,7 +1962,7 @@
       <c r="D4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -2041,12 +2038,12 @@
         <v>48</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="16" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -2127,7 +2124,7 @@
       <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="16" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
@@ -2240,48 +2237,48 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>61</v>
       </c>
       <c r="L2" s="12"/>
@@ -2296,66 +2293,66 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="C3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2407,32 +2404,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>74</v>
       </c>
       <c r="H2" s="12"/>
@@ -2448,22 +2445,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -2473,22 +2470,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -2560,56 +2557,56 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="18" t="s">
         <v>85</v>
       </c>
       <c r="M2" s="12"/>
@@ -2622,155 +2619,155 @@
       <c r="XFC2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="K3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="19" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="K4" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="19" t="s">
         <v>100</v>
       </c>
       <c r="XFD4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="K5" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="19" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="K6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="19" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2824,36 +2821,36 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>112</v>
       </c>
       <c r="XEU2" s="3"/>
@@ -2868,48 +2865,48 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>78</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>78</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="19" t="n">
         <v>0.583</v>
       </c>
     </row>
@@ -3294,7 +3291,7 @@
       <c r="C5" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="22" t="s">
         <v>155</v>
       </c>
       <c r="E5" s="22" t="s">

--- a/src/flychams_common/config/Configuration-Single-Agent.xlsx
+++ b/src/flychams_common/config/Configuration-Single-Agent.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -544,7 +544,7 @@
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -605,13 +605,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -712,7 +705,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -745,7 +738,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -757,16 +750,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1430,7 +1419,7 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
@@ -1549,92 +1538,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>145</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="22" t="b">
+      <c r="C3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="22" t="b">
+      <c r="E3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="G3" s="22" t="b">
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1688,12 +1677,12 @@
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
       <c r="E1" s="12"/>
       <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
@@ -1723,7 +1712,7 @@
       <c r="C3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1737,7 +1726,7 @@
       <c r="C4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1777,15 +1766,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -1881,7 +1870,7 @@
       <c r="D3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="15" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -1962,7 +1951,7 @@
       <c r="D4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -2043,7 +2032,7 @@
       <c r="D5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="15" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="9" t="s">
@@ -2124,7 +2113,7 @@
       <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="9" t="s">
@@ -2237,48 +2226,48 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>61</v>
       </c>
       <c r="L2" s="12"/>
@@ -2293,66 +2282,66 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2404,32 +2393,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>74</v>
       </c>
       <c r="H2" s="12"/>
@@ -2445,22 +2434,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -2470,22 +2459,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -2557,56 +2546,56 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="17" t="s">
         <v>85</v>
       </c>
       <c r="M2" s="12"/>
@@ -2619,155 +2608,155 @@
       <c r="XFC2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="19" t="n">
+      <c r="I4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="18" t="s">
         <v>100</v>
       </c>
       <c r="XFD4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" s="19" t="n">
+      <c r="I5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="18" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="18" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2821,36 +2810,36 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>112</v>
       </c>
       <c r="XEU2" s="3"/>
@@ -2865,48 +2854,48 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G4" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
@@ -2964,140 +2953,140 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="20" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D3" s="22" t="n">
+      <c r="D3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="22" t="b">
+      <c r="F3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="H3" s="22" t="b">
+      <c r="H3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="J3" s="22" t="b">
+      <c r="J3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="L3" s="22" t="b">
+      <c r="L3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="N3" s="22" t="n">
+      <c r="N3" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="22" t="n">
+      <c r="O3" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="22" t="n">
+      <c r="P3" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="22" t="n">
+      <c r="Q3" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="22" t="n">
+      <c r="R3" s="21" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3157,52 +3146,52 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>145</v>
       </c>
       <c r="XFB2" s="3"/>
@@ -3210,110 +3199,110 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="22" t="b">
+      <c r="G3" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G4" s="22" t="b">
+      <c r="G4" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="I4" s="22" t="n">
+      <c r="I4" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="22" t="n">
+      <c r="J4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="21" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="22" t="b">
+      <c r="G5" s="21" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
     </row>

--- a/src/flychams_common/config/Configuration-Single-Agent.xlsx
+++ b/src/flychams_common/config/Configuration-Single-Agent.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>

--- a/src/flychams_common/config/Configuration-Single-Agent.xlsx
+++ b/src/flychams_common/config/Configuration-Single-Agent.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="169">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -64,39 +64,39 @@
     <t xml:space="preserve">StartHour</t>
   </si>
   <si>
+    <t xml:space="preserve">MISSION00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuration A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENVIRONMENT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-150.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(30.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13/12/2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16:30:00)</t>
+  </si>
+  <si>
     <t xml:space="preserve">X</t>
   </si>
   <si>
-    <t xml:space="preserve">MISSION00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configuration A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENVIRONMENT00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-150.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(30.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13/12/2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(16:30:00)</t>
-  </si>
-  <si>
     <t xml:space="preserve">MISSION01</t>
   </si>
   <si>
@@ -145,10 +145,25 @@
     <t xml:space="preserve">TARGET00</t>
   </si>
   <si>
-    <t xml:space="preserve">Target Configuration L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP00</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Default</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Configuration (4 Clusters)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Human</t>
@@ -157,40 +172,7 @@
     <t xml:space="preserve">High</t>
   </si>
   <si>
-    <t xml:space="preserve">TargetConfigurationL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TARGET01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target Configuration L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TargetConfigurationL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TARGET02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target Configuration L3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TargetConfigurationL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TARGET03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target Configuration L4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TargetConfigurationL4</t>
+    <t xml:space="preserve">Default</t>
   </si>
   <si>
     <t xml:space="preserve">AGENT CONFIGURATION</t>
@@ -349,13 +331,37 @@
     <t xml:space="preserve">MULTICAMERA03</t>
   </si>
   <si>
+    <t xml:space="preserve">Tracking Head 3 Multi-Camera (2 Cameras)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=180.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT00/MULTICAMERA03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Head 4 Multi-Camera (2 Cameras)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=270.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT00/MULTICAMERA04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA05</t>
+  </si>
+  <si>
     <t xml:space="preserve">Central Head Multi-Window (2 Windows)</t>
   </si>
   <si>
     <t xml:space="preserve">CAM02</t>
   </si>
   <si>
-    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT01/MULTICAMERA03</t>
+    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT01/MULTICAMERA05</t>
   </si>
   <si>
     <t xml:space="preserve">Resolution [pix]</t>
@@ -380,6 +386,21 @@
   </si>
   <si>
     <t xml:space="preserve">MULTIWINDOW01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 2 Multi-Window (2 Windows)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 3 Multi-Window (2 Windows)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 4 Multi-Window (2 Windows)</t>
   </si>
   <si>
     <t xml:space="preserve">HARDWARE CATALOGS</t>
@@ -539,12 +560,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -612,6 +634,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -705,7 +733,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -766,6 +794,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -791,6 +823,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -959,8 +995,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table210" displayName="Table210" ref="A2:J6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A2:J6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table210" displayName="Table210" ref="A2:J8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:J8"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
@@ -1104,37 +1140,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
@@ -1274,7 +1310,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="21" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.44"/>
@@ -1339,38 +1375,36 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -1419,7 +1453,9 @@
       <c r="BD3" s="12"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
@@ -1427,28 +1463,28 @@
         <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>15</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -1524,7 +1560,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="2" width="29.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.25"/>
@@ -1538,92 +1574,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="I2" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="J2" s="20" t="s">
+      <c r="H2" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>145</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>146</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="21" t="b">
+      <c r="A3" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" s="21" t="b">
+      <c r="D3" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="G3" s="21" t="b">
+      <c r="F3" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="I3" s="21" t="n">
+      <c r="H3" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="21" t="n">
+      <c r="J3" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="22" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1664,7 +1700,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.54"/>
@@ -1704,7 +1740,7 @@
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>27</v>
@@ -1755,7 +1791,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:BM1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="38.38"/>
@@ -1857,27 +1893,27 @@
       <c r="BL2" s="7"/>
       <c r="BM2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>42</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -1936,251 +1972,10 @@
       <c r="BJ3" s="12"/>
       <c r="BK3" s="12"/>
       <c r="BL3" s="12"/>
-      <c r="BM3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12"/>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
-      <c r="AH4" s="12"/>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="12"/>
-      <c r="AM4" s="12"/>
-      <c r="AN4" s="12"/>
-      <c r="AO4" s="12"/>
-      <c r="AP4" s="12"/>
-      <c r="AQ4" s="12"/>
-      <c r="AR4" s="12"/>
-      <c r="AS4" s="12"/>
-      <c r="AT4" s="12"/>
-      <c r="AU4" s="12"/>
-      <c r="AV4" s="12"/>
-      <c r="AW4" s="12"/>
-      <c r="AX4" s="12"/>
-      <c r="AY4" s="12"/>
-      <c r="AZ4" s="12"/>
-      <c r="BA4" s="12"/>
-      <c r="BB4" s="12"/>
-      <c r="BC4" s="12"/>
-      <c r="BD4" s="12"/>
-      <c r="BE4" s="12"/>
-      <c r="BF4" s="12"/>
-      <c r="BG4" s="12"/>
-      <c r="BH4" s="12"/>
-      <c r="BI4" s="12"/>
-      <c r="BJ4" s="12"/>
-      <c r="BK4" s="12"/>
-      <c r="BL4" s="12"/>
-      <c r="BM4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12"/>
-      <c r="AF5" s="12"/>
-      <c r="AG5" s="12"/>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="12"/>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="12"/>
-      <c r="AM5" s="12"/>
-      <c r="AN5" s="12"/>
-      <c r="AO5" s="12"/>
-      <c r="AP5" s="12"/>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="12"/>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="12"/>
-      <c r="AX5" s="12"/>
-      <c r="AY5" s="12"/>
-      <c r="AZ5" s="12"/>
-      <c r="BA5" s="12"/>
-      <c r="BB5" s="12"/>
-      <c r="BC5" s="12"/>
-      <c r="BD5" s="12"/>
-      <c r="BE5" s="12"/>
-      <c r="BF5" s="12"/>
-      <c r="BG5" s="12"/>
-      <c r="BH5" s="12"/>
-      <c r="BI5" s="12"/>
-      <c r="BJ5" s="12"/>
-      <c r="BK5" s="12"/>
-      <c r="BL5" s="12"/>
-      <c r="BM5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="12"/>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="12"/>
-      <c r="AH6" s="12"/>
-      <c r="AI6" s="12"/>
-      <c r="AJ6" s="12"/>
-      <c r="AK6" s="12"/>
-      <c r="AL6" s="12"/>
-      <c r="AM6" s="12"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="12"/>
-      <c r="AQ6" s="12"/>
-      <c r="AR6" s="12"/>
-      <c r="AS6" s="12"/>
-      <c r="AT6" s="12"/>
-      <c r="AU6" s="12"/>
-      <c r="AV6" s="12"/>
-      <c r="AW6" s="12"/>
-      <c r="AX6" s="12"/>
-      <c r="AY6" s="12"/>
-      <c r="AZ6" s="12"/>
-      <c r="BA6" s="12"/>
-      <c r="BB6" s="12"/>
-      <c r="BC6" s="12"/>
-      <c r="BD6" s="12"/>
-      <c r="BE6" s="12"/>
-      <c r="BF6" s="12"/>
-      <c r="BG6" s="12"/>
-      <c r="BH6" s="12"/>
-      <c r="BI6" s="12"/>
-      <c r="BJ6" s="12"/>
-      <c r="BK6" s="12"/>
-      <c r="BL6" s="12"/>
-      <c r="BM6" s="3"/>
-    </row>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2207,7 +2002,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -2226,49 +2021,49 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>61</v>
+      <c r="D2" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
@@ -2282,66 +2077,66 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="18" t="n">
+      <c r="A3" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="18" t="n">
+      <c r="I3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="A4" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4" s="18" t="n">
+      <c r="D4" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="19" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2377,7 +2172,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -2393,33 +2188,33 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>74</v>
+      <c r="C2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>62</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
@@ -2434,22 +2229,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F3" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -2459,22 +2254,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="18" t="n">
+      <c r="A4" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -2528,7 +2323,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -2546,57 +2341,57 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>85</v>
+      <c r="K2" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>73</v>
       </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
@@ -2608,160 +2403,236 @@
       <c r="XFC2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="H4" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="I4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="XFD4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="C5" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H5" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="18" t="n">
+    </row>
+    <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="XFD6" s="0"/>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="XFD7" s="0"/>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="K8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="I4" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K4" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="XFD4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="18" t="s">
+      <c r="L8" s="19" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2796,7 +2667,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="57.21"/>
@@ -2810,37 +2681,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>112</v>
+      <c r="C2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>108</v>
       </c>
       <c r="XEU2" s="3"/>
       <c r="XEV2" s="3"/>
@@ -2854,53 +2725,99 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="19" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C4" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="19" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="C5" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="18" t="n">
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G5" s="19" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="XFD5" s="0"/>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="18" t="n">
+      <c r="B6" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="19" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G6" s="19" t="n">
         <v>0.583</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="XFD6" s="0"/>
+    </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2935,7 +2852,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="34.63"/>
@@ -2953,140 +2870,140 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="L2" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="M2" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="N2" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="O2" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="P2" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="Q2" s="21" t="s">
         <v>132</v>
       </c>
+      <c r="R2" s="21" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="C3" s="21" t="s">
+      <c r="A3" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D3" s="21" t="n">
+      <c r="C3" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="21" t="b">
+      <c r="F3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="H3" s="21" t="b">
+      <c r="G3" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="J3" s="21" t="b">
+      <c r="I3" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="L3" s="21" t="b">
+      <c r="K3" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="L3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="N3" s="21" t="n">
+      <c r="M3" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="N3" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="21" t="n">
+      <c r="O3" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="21" t="n">
+      <c r="P3" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="21" t="n">
+      <c r="Q3" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="21" t="n">
+      <c r="R3" s="22" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3130,7 +3047,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="63.93"/>
@@ -3146,163 +3063,163 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F2" s="20" t="s">
+      <c r="D2" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>145</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>146</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="C3" s="21" t="s">
+      <c r="A3" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="E3" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="21" t="b">
+      <c r="F3" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" s="21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" s="21" t="b">
+      <c r="G4" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="I4" s="21" t="n">
+      <c r="H4" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="22" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="21" t="s">
+      <c r="A5" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="21" t="s">
+      <c r="C5" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="21" t="b">
+      <c r="E5" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="23" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="I5" s="21" t="n">
+      <c r="H5" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="I5" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="22" t="n">
         <v>5</v>
       </c>
     </row>

--- a/src/flychams_common/config/Configuration-Single-Agent.xlsx
+++ b/src/flychams_common/config/Configuration-Single-Agent.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="171">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -145,6 +145,187 @@
     <t xml:space="preserve">TARGET00</t>
   </si>
   <si>
+    <t xml:space="preserve">Default Configuration (4 Clusters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT CONFIGURATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrackingID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DroneID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orientation [°]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxAltitude [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SafetyRadius [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BatteryCapacity [mAh]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type A Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRONE00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(X=0.0, Y=0.0, Z=0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Roll=0.0, Pitch=0.0, Yaw=0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENT01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type B Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRACKING01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ObservationSetID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MinTargetSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxTargetSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RefTargetSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Camera Tracking (2 Cameras)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Window Tracking (2 Windows)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CameraID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GimbalID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MinFocal [mm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxFocal [mm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RefFocal [mm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SourceStreamURL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central Head Multi-Camera (2 Cameras)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAM00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIM00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(X=0.0, Y=0.0, Z=-0.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=90.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT00/MULTICAMERA00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Head 1 Multi-Camera (2 Cameras)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAM01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(X=0.19, Y=0.0, Z=-0.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT00/MULTICAMERA01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Head 2 Multi-Camera (2 Cameras)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(X=-0.19, Y=0.0, Z=-0.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT00/MULTICAMERA02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTICAMERA03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Head 3 Multi-Camera (2 Cameras)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(X=0.0, Y=</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
@@ -152,7 +333,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Default</t>
+      <t xml:space="preserve">0.19</t>
     </r>
     <r>
       <rPr>
@@ -162,178 +343,10 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Configuration (4 Clusters)</t>
+      <t xml:space="preserve">, Z=-0.04)</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Human</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Default</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT CONFIGURATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrackingID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DroneID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Position [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orientation [°]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxAltitude [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SafetyRadius [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BatteryCapacity [mAh]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type A Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRONE00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(X=0.0, Y=0.0, Z=0.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Roll=0.0, Pitch=0.0, Yaw=0.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGENT01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type B Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRACKING01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ObservationSetID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MinTargetSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxTargetSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RefTargetSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Camera Tracking (2 Cameras)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Window Tracking (2 Windows)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CameraID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GimbalID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MinFocal [mm]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxFocal [mm]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RefFocal [mm]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SourceStreamURL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central Head Multi-Camera (2 Cameras)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAM00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIM00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(X=0.0, Y=0.0, Z=-0.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=90.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT00/MULTICAMERA00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Head 1 Multi-Camera (2 Cameras)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAM01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(X=0.3, Y=0.0, Z=-0.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=0.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT00/MULTICAMERA01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Head 2 Multi-Camera (2 Cameras)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(X=0.0, Y=0.3, Z=-0.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rtsp://127.0.0.1:8554/AGENT00/MULTICAMERA02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTICAMERA03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Head 3 Multi-Camera (2 Cameras)</t>
-  </si>
-  <si>
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=180.0)</t>
   </si>
   <si>
@@ -344,6 +357,37 @@
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 4 Multi-Camera (2 Cameras)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(X=0.0, Y=-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">0.19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, Z=-0.04)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=270.0)</t>
@@ -733,7 +777,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -791,10 +835,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1574,92 +1614,92 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="I2" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="K2" s="21" t="s">
+      <c r="G2" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="I2" s="20" t="s">
         <v>146</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>148</v>
       </c>
       <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="C3" s="23" t="b">
+      <c r="B3" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" s="23" t="b">
+      <c r="D3" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="G3" s="23" t="b">
+      <c r="F3" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="I3" s="22" t="n">
+      <c r="H3" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="I3" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="21" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1897,7 +1937,7 @@
       <c r="A3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -1906,7 +1946,7 @@
       <c r="D3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="15" t="n">
         <v>16</v>
       </c>
       <c r="F3" s="9" t="s">
@@ -2021,48 +2061,48 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>49</v>
       </c>
       <c r="L2" s="12"/>
@@ -2077,66 +2117,66 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="19" t="n">
+      <c r="H3" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="18" t="n">
         <v>300</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2188,32 +2228,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>62</v>
       </c>
       <c r="H2" s="12"/>
@@ -2229,22 +2269,22 @@
       <c r="XFD2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
@@ -2254,22 +2294,22 @@
       <c r="XEY3" s="3"/>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
@@ -2341,56 +2381,56 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="17" t="s">
         <v>73</v>
       </c>
       <c r="M2" s="12"/>
@@ -2403,234 +2443,234 @@
       <c r="XFC2" s="12"/>
     </row>
     <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="19" t="n">
+      <c r="I3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="J3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="K3" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="18" t="s">
         <v>88</v>
       </c>
       <c r="XFD4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="18" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="19" t="s">
+      <c r="G6" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="H6" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="J6" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="K6" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="XFD6" s="0"/>
+      <c r="L6" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="XFD6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="B7" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="XFD7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="I7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="XFD7" s="0"/>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="19" t="s">
-        <v>104</v>
+      <c r="L8" s="18" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -2681,37 +2721,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>108</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>110</v>
       </c>
       <c r="XEU2" s="3"/>
       <c r="XEV2" s="3"/>
@@ -2725,98 +2765,96 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" s="19" t="n">
+      <c r="D3" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="E4" s="18" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0.583</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="19" t="n">
+      <c r="D5" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G5" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="19" t="s">
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" s="19" t="n">
+      <c r="D6" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="18" t="n">
         <v>0.167</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G6" s="18" t="n">
         <v>0.583</v>
       </c>
-      <c r="XFD5" s="0"/>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="XFD6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2870,140 +2908,140 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="L2" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="M2" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="N2" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="O2" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="P2" s="20" t="s">
         <v>133</v>
       </c>
+      <c r="Q2" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="22" t="n">
+      <c r="B3" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="23" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="H3" s="23" t="b">
+      <c r="G3" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="J3" s="23" t="b">
+      <c r="I3" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="L3" s="23" t="b">
+      <c r="K3" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="N3" s="22" t="n">
+      <c r="M3" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="N3" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="22" t="n">
+      <c r="O3" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="22" t="n">
+      <c r="P3" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="22" t="n">
+      <c r="Q3" s="21" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="22" t="n">
+      <c r="R3" s="21" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3063,163 +3101,163 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
+      <c r="A1" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="G2" s="21" t="s">
+      <c r="D2" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>146</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>148</v>
       </c>
       <c r="XFB2" s="3"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="23" t="b">
+      <c r="E3" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="I3" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" s="22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="F4" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="G4" s="23" t="b">
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="G5" s="23" t="b">
+      <c r="F5" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="I5" s="22" t="n">
+      <c r="H5" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="21" t="n">
         <v>5</v>
       </c>
     </row>
